--- a/FileStructure.xlsx
+++ b/FileStructure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kvaughn/GitHub/ontology-its-location/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{873B2404-02A0-A148-837E-062C1AF99AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E5B077-E4AB-7B43-9102-AF8B42A2A2B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57940" yWindow="1280" windowWidth="28820" windowHeight="18100" activeTab="2" xr2:uid="{B2010265-CA75-7E45-9BAB-ECA6C63CF7DC}"/>
+    <workbookView xWindow="32740" yWindow="840" windowWidth="28820" windowHeight="18100" activeTab="2" xr2:uid="{B2010265-CA75-7E45-9BAB-ECA6C63CF7DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="341">
   <si>
     <t>AreaLocationPattern</t>
   </si>
@@ -1045,43 +1045,55 @@
     <t>direction of traffic flow; direction of navigation compared to node definition; named direction</t>
   </si>
   <si>
-    <t>LinearRepresentation</t>
-  </si>
-  <si>
-    <t>Geometry</t>
-  </si>
-  <si>
-    <t>Feature</t>
-  </si>
-  <si>
-    <t>(could be less than a segment)</t>
-  </si>
-  <si>
-    <t>Infrastructure concept</t>
-  </si>
-  <si>
-    <t>LinearLocation can be MultiLineString</t>
-  </si>
-  <si>
     <t>LinearByPoints</t>
   </si>
   <si>
     <t>LinearByCode</t>
   </si>
   <si>
-    <t>LinearRing</t>
-  </si>
-  <si>
-    <t>LinearString</t>
-  </si>
-  <si>
-    <t>MultiLineString</t>
-  </si>
-  <si>
     <t>LineElement + its-transport-network</t>
   </si>
   <si>
     <t>PointByLinearOffset</t>
+  </si>
+  <si>
+    <t>cdm3</t>
+  </si>
+  <si>
+    <t>Offset</t>
+  </si>
+  <si>
+    <t>OffsetDistance can be Percentage or Length</t>
+  </si>
+  <si>
+    <t>LineLocation</t>
+  </si>
+  <si>
+    <t>ReferencePoint</t>
+  </si>
+  <si>
+    <t>AreaRepresentation</t>
+  </si>
+  <si>
+    <t>AreaByCircle</t>
+  </si>
+  <si>
+    <t>AreaByGrid</t>
+  </si>
+  <si>
+    <t>AreaByCode</t>
+  </si>
+  <si>
+    <t>AreaByMultiPolygon</t>
+  </si>
+  <si>
+    <t>AreaByPolygon</t>
+  </si>
+  <si>
+    <t>AreaByRectangle</t>
+  </si>
+  <si>
+    <t>AreaByLinearBoundaries</t>
   </si>
 </sst>
 </file>
@@ -2709,7 +2721,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7159C67-C111-F245-9004-71E877049404}">
-  <dimension ref="A1:L105"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.33203125" bestFit="1" customWidth="1"/>
@@ -2742,6 +2754,9 @@
       <c r="C2" t="s">
         <v>271</v>
       </c>
+      <c r="E2" t="s">
+        <v>2</v>
+      </c>
       <c r="I2" t="s">
         <v>0</v>
       </c>
@@ -2756,6 +2771,9 @@
       <c r="C3" t="s">
         <v>296</v>
       </c>
+      <c r="E3" t="s">
+        <v>333</v>
+      </c>
       <c r="I3" t="s">
         <v>22</v>
       </c>
@@ -2764,25 +2782,28 @@
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>253</v>
       </c>
       <c r="C4" t="s">
         <v>296</v>
       </c>
-      <c r="I4" t="s">
-        <v>81</v>
+      <c r="E4" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C5" t="s">
         <v>296</v>
+      </c>
+      <c r="E5" t="s">
+        <v>336</v>
       </c>
       <c r="I5" t="s">
         <v>243</v>
@@ -2792,39 +2813,42 @@
       <c r="A6" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>260</v>
       </c>
       <c r="C6" t="s">
         <v>296</v>
       </c>
-      <c r="I6" t="s">
-        <v>6</v>
+      <c r="E6" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>261</v>
       </c>
       <c r="C7" t="s">
         <v>296</v>
       </c>
-      <c r="I7" t="s">
-        <v>8</v>
+      <c r="E7" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>262</v>
       </c>
       <c r="C8" t="s">
         <v>296</v>
+      </c>
+      <c r="E8" t="s">
+        <v>338</v>
       </c>
       <c r="I8" t="s">
         <v>5</v>
@@ -2834,30 +2858,36 @@
       <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
         <v>296</v>
+      </c>
+      <c r="E9" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
         <v>296</v>
+      </c>
+      <c r="E10" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B11" t="s">
-        <v>272</v>
+      <c r="B11" s="1" t="s">
+        <v>333</v>
       </c>
       <c r="C11" t="s">
         <v>296</v>
@@ -2867,7 +2897,7 @@
       <c r="A12" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>275</v>
       </c>
       <c r="C12" t="s">
@@ -2889,7 +2919,7 @@
       <c r="A14" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>278</v>
       </c>
       <c r="C14" t="s">
@@ -2900,7 +2930,7 @@
       <c r="A15" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>281</v>
       </c>
       <c r="C15" t="s">
@@ -2911,7 +2941,7 @@
       <c r="A16" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>282</v>
       </c>
       <c r="C16" t="s">
@@ -2922,7 +2952,7 @@
       <c r="A17" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>282</v>
       </c>
       <c r="C17" t="s">
@@ -2933,7 +2963,7 @@
       <c r="A18" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>287</v>
       </c>
       <c r="C18" t="s">
@@ -2944,7 +2974,7 @@
       <c r="A19" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C19" t="s">
@@ -2955,7 +2985,7 @@
       <c r="A20" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>275</v>
       </c>
       <c r="C20" t="s">
@@ -2966,7 +2996,7 @@
       <c r="A21" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C21" t="s">
@@ -3234,7 +3264,7 @@
         <v>265</v>
       </c>
       <c r="C45" t="s">
-        <v>297</v>
+        <v>328</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
@@ -3245,7 +3275,7 @@
         <v>266</v>
       </c>
       <c r="C46" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
@@ -3256,7 +3286,7 @@
         <v>268</v>
       </c>
       <c r="C47" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -3267,10 +3297,10 @@
         <v>269</v>
       </c>
       <c r="C48" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>189</v>
       </c>
@@ -3278,10 +3308,10 @@
         <v>267</v>
       </c>
       <c r="C49" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
         <v>192</v>
       </c>
@@ -3289,10 +3319,10 @@
         <v>322</v>
       </c>
       <c r="C50" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>43</v>
       </c>
@@ -3306,7 +3336,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>207</v>
       </c>
@@ -3317,178 +3347,139 @@
         <v>297</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C53" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C54" t="s">
         <v>297</v>
       </c>
-      <c r="I54" t="s">
-        <v>324</v>
-      </c>
-      <c r="K54" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C55" t="s">
         <v>297</v>
       </c>
-      <c r="I55" t="s">
-        <v>25</v>
-      </c>
-      <c r="K55" t="s">
-        <v>326</v>
-      </c>
-      <c r="L55" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>236</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C56" t="s">
         <v>297</v>
       </c>
-      <c r="I56" t="s">
-        <v>188</v>
-      </c>
-      <c r="K56" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C57" t="s">
         <v>297</v>
       </c>
-      <c r="I57" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C58" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="C59" t="s">
         <v>299</v>
       </c>
-      <c r="I59" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="C60" t="s">
         <v>299</v>
       </c>
-      <c r="I60" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>206</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C61" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C62" t="s">
         <v>297</v>
       </c>
-      <c r="I62" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>205</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="C63" t="s">
         <v>297</v>
       </c>
-      <c r="I63" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>210</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="C64" t="s">
         <v>297</v>
       </c>
-      <c r="I64" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>182</v>
       </c>
@@ -3499,7 +3490,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>214</v>
       </c>
@@ -3510,7 +3501,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>181</v>
       </c>
@@ -3521,7 +3512,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>183</v>
       </c>
@@ -3531,8 +3522,11 @@
       <c r="C68" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="H68" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>53</v>
       </c>
@@ -3542,8 +3536,14 @@
       <c r="C69" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="F69" t="s">
+        <v>36</v>
+      </c>
+      <c r="G69" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>177</v>
       </c>
@@ -3554,7 +3554,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>178</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>179</v>
       </c>
@@ -3576,7 +3576,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>57</v>
       </c>
@@ -3587,7 +3587,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>198</v>
       </c>
@@ -3598,7 +3598,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>209</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>211</v>
       </c>
@@ -3619,8 +3619,11 @@
       <c r="C76" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="F76" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>212</v>
       </c>
@@ -3630,8 +3633,11 @@
       <c r="C77" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="F77" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>218</v>
       </c>
@@ -3641,8 +3647,11 @@
       <c r="C78" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="F78" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>32</v>
       </c>
@@ -3653,7 +3662,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>230</v>
       </c>
